--- a/catalog-public.xlsx
+++ b/catalog-public.xlsx
@@ -434,16 +434,16 @@
     <t>Комплект накладок на боковые зеркала для Haval Dargo / Big Dog. В набор входят верхние накладки с козырьком и нижние накладки на корпус зеркала. Такой комплект помогает защитить верхнюю и нижнюю часть зеркала от мелких царапин и брызг, а также делает внешний вид автомобиля более аккуратным и завершённым.</t>
   </si>
   <si>
-    <t>images/Deflector_1.png; images/Deflector_2.png; images/Deflector_3.png; images/Deflector_4.png.</t>
-  </si>
-  <si>
-    <t>image/shapka_deflector_1.svg.</t>
-  </si>
-  <si>
     <t>image/shapka_nakladka_1.png</t>
   </si>
   <si>
-    <t>images/Nakladka_1.png; images/Nakladka_2.png; images/Nakladka_3.png.</t>
+    <t>image/shapka_deflector_1.svg</t>
+  </si>
+  <si>
+    <t>images/Deflector_1.png; images/Deflector_2.png; images/Deflector_3.png; images/Deflector_4.png</t>
+  </si>
+  <si>
+    <t>images/Nakladka_1.png; images/Nakladka_2.png; images/Nakladka_3.png</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1176,7 @@
         <v>138</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>132</v>
@@ -1217,7 +1217,7 @@
         <v>19</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>140</v>

--- a/catalog-public.xlsx
+++ b/catalog-public.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17990"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17980"/>
   </bookViews>
   <sheets>
     <sheet name="Сайт_экспорт" sheetId="1" r:id="rId1"/>
@@ -434,16 +434,16 @@
     <t>Комплект накладок на боковые зеркала для Haval Dargo / Big Dog. В набор входят верхние накладки с козырьком и нижние накладки на корпус зеркала. Такой комплект помогает защитить верхнюю и нижнюю часть зеркала от мелких царапин и брызг, а также делает внешний вид автомобиля более аккуратным и завершённым.</t>
   </si>
   <si>
-    <t>image/shapka_nakladka_1.png</t>
-  </si>
-  <si>
-    <t>image/shapka_deflector_1.svg</t>
-  </si>
-  <si>
     <t>images/Deflector_1.png; images/Deflector_2.png; images/Deflector_3.png; images/Deflector_4.png</t>
   </si>
   <si>
     <t>images/Nakladka_1.png; images/Nakladka_2.png; images/Nakladka_3.png</t>
+  </si>
+  <si>
+    <t>images/shapka_deflector_1.svg</t>
+  </si>
+  <si>
+    <t>images/shapka_nakladka_1.png</t>
   </si>
 </sst>
 </file>
@@ -1173,10 +1173,10 @@
         <v>19</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>132</v>
@@ -1217,10 +1217,10 @@
         <v>19</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>136</v>

--- a/catalog-public.xlsx
+++ b/catalog-public.xlsx
@@ -9,19 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17980"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17980" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Сайт_экспорт" sheetId="1" r:id="rId1"/>
     <sheet name="Справочник" sheetId="2" r:id="rId2"/>
-    <sheet name="Инструкция" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="132">
   <si>
     <t>id</t>
   </si>
@@ -381,33 +380,6 @@
   </si>
   <si>
     <t>Датчики давления TPMS</t>
-  </si>
-  <si>
-    <t>Как использовать catalog-public.xlsx</t>
-  </si>
-  <si>
-    <t>1. Заполняй только лист «Сайт_экспорт».</t>
-  </si>
-  <si>
-    <t>2. В публичный файл не добавляй закупочные цены, маржу, прибыль и внутренние расчёты.</t>
-  </si>
-  <si>
-    <t>3. image — одна картинка для карточки каталога, например images/deflector-card.png.</t>
-  </si>
-  <si>
-    <t>4. images — галерея на странице товара через точку с запятой, например images/deflector-1.png; images/deflector-2.png.</t>
-  </si>
-  <si>
-    <t>5. testedByUs: TRUE/FALSE. TRUE покажет бейдж «Проверено нами».</t>
-  </si>
-  <si>
-    <t>6. supplierType: factory / supplier / unknown.</t>
-  </si>
-  <si>
-    <t>7. После обновления файла запускай GitHub Actions workflow для генерации js/products.js.</t>
-  </si>
-  <si>
-    <t>8. Файлы картинок должны лежать в папке images и называться латиницей без пробелов.</t>
   </si>
   <si>
     <t>Дефлекторы окон (на 4 окна)</t>
@@ -450,7 +422,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -462,17 +434,11 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF11100E"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,11 +448,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF101113"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8A55A"/>
       </patternFill>
     </fill>
   </fills>
@@ -501,17 +462,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -749,7 +707,7 @@
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -761,10 +719,10 @@
       <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="3">
         <v>2799</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>672</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -789,7 +747,7 @@
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -801,10 +759,10 @@
       <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3">
         <v>1299</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>1960</v>
       </c>
       <c r="G3" s="2" t="s">
@@ -829,7 +787,7 @@
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -841,10 +799,10 @@
       <c r="D4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="3">
         <v>909</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>112</v>
       </c>
       <c r="G4" s="2" t="s">
@@ -869,7 +827,7 @@
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -881,10 +839,10 @@
       <c r="D5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>1899</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>140</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -909,7 +867,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="28">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -921,10 +879,10 @@
       <c r="D6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>1199</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>168</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -949,7 +907,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="28">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -961,10 +919,10 @@
       <c r="D7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>2799</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>252</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -989,7 +947,7 @@
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1001,10 +959,10 @@
       <c r="D8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>14699</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>8652</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -1027,7 +985,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="28">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1039,10 +997,10 @@
       <c r="D9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>10999</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>4032</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -1065,7 +1023,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="28">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1077,10 +1035,10 @@
       <c r="D10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>1199</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>392</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -1105,7 +1063,7 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="28">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1117,10 +1075,10 @@
       <c r="D11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>1199</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>392</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -1145,11 +1103,11 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="70">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>24</v>
@@ -1157,29 +1115,29 @@
       <c r="D12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>1620</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="3">
         <v>1006</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="K12" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>66</v>
@@ -1189,11 +1147,11 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="98">
-      <c r="A13" s="4">
+      <c r="A13" s="3">
         <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>24</v>
@@ -1201,29 +1159,29 @@
       <c r="D13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="3">
         <v>3099</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="3">
         <v>340</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>21</v>
@@ -1233,14 +1191,14 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="4">
+      <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
@@ -1257,14 +1215,14 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="4">
+      <c r="A15" s="3">
         <v>13</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
@@ -1281,14 +1239,14 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="4">
+      <c r="A16" s="3">
         <v>14</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
@@ -1305,14 +1263,14 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="4">
+      <c r="A17" s="3">
         <v>15</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
@@ -1329,14 +1287,14 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="4">
+      <c r="A18" s="3">
         <v>16</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
@@ -1353,14 +1311,14 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="4">
+      <c r="A19" s="3">
         <v>17</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
@@ -1377,14 +1335,14 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="4">
+      <c r="A20" s="3">
         <v>18</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
@@ -1401,14 +1359,14 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="4">
+      <c r="A21" s="3">
         <v>19</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
@@ -1425,14 +1383,14 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="4">
+      <c r="A22" s="3">
         <v>20</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
@@ -1449,14 +1407,14 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="4">
+      <c r="A23" s="3">
         <v>21</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
@@ -1473,14 +1431,14 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="4">
+      <c r="A24" s="3">
         <v>22</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
@@ -1497,14 +1455,14 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="4">
+      <c r="A25" s="3">
         <v>23</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
@@ -1521,14 +1479,14 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="4">
+      <c r="A26" s="3">
         <v>24</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
@@ -1545,14 +1503,14 @@
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="4">
+      <c r="A27" s="3">
         <v>25</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
@@ -1569,12 +1527,12 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="4"/>
+      <c r="A28" s="3"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
@@ -1591,12 +1549,12 @@
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="4"/>
+      <c r="A29" s="3"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
@@ -1613,12 +1571,12 @@
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="4"/>
+      <c r="A30" s="3"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
@@ -1635,12 +1593,12 @@
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="4"/>
+      <c r="A31" s="3"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
@@ -1657,12 +1615,12 @@
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="4"/>
+      <c r="A32" s="3"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
@@ -1679,12 +1637,12 @@
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="4"/>
+      <c r="A33" s="3"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
@@ -1701,12 +1659,12 @@
       </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="4"/>
+      <c r="A34" s="3"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
@@ -1723,12 +1681,12 @@
       </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="4"/>
+      <c r="A35" s="3"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
@@ -1745,12 +1703,12 @@
       </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="4"/>
+      <c r="A36" s="3"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
@@ -1767,12 +1725,12 @@
       </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="4"/>
+      <c r="A37" s="3"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
@@ -1789,12 +1747,12 @@
       </c>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="4"/>
+      <c r="A38" s="3"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
@@ -1811,12 +1769,12 @@
       </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="4"/>
+      <c r="A39" s="3"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
@@ -1833,12 +1791,12 @@
       </c>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="4"/>
+      <c r="A40" s="3"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2" t="s">
@@ -1855,12 +1813,12 @@
       </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="4"/>
+      <c r="A41" s="3"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
@@ -1877,12 +1835,12 @@
       </c>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="4"/>
+      <c r="A42" s="3"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2" t="s">
@@ -1899,12 +1857,12 @@
       </c>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="4"/>
+      <c r="A43" s="3"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
@@ -1921,12 +1879,12 @@
       </c>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="4"/>
+      <c r="A44" s="3"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
@@ -1943,12 +1901,12 @@
       </c>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="4"/>
+      <c r="A45" s="3"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
@@ -1965,12 +1923,12 @@
       </c>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="4"/>
+      <c r="A46" s="3"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
@@ -1987,12 +1945,12 @@
       </c>
     </row>
     <row r="47" spans="1:14">
-      <c r="A47" s="4"/>
+      <c r="A47" s="3"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
@@ -2009,12 +1967,12 @@
       </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="4"/>
+      <c r="A48" s="3"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
@@ -2031,12 +1989,12 @@
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="4"/>
+      <c r="A49" s="3"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
@@ -2053,12 +2011,12 @@
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="4"/>
+      <c r="A50" s="3"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
@@ -2075,12 +2033,12 @@
       </c>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" s="4"/>
+      <c r="A51" s="3"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
@@ -2097,12 +2055,12 @@
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="4"/>
+      <c r="A52" s="3"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
@@ -2119,12 +2077,12 @@
       </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="4"/>
+      <c r="A53" s="3"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
@@ -2141,12 +2099,12 @@
       </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="4"/>
+      <c r="A54" s="3"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
@@ -2163,12 +2121,12 @@
       </c>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="4"/>
+      <c r="A55" s="3"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
@@ -2185,12 +2143,12 @@
       </c>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" s="4"/>
+      <c r="A56" s="3"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
@@ -2207,12 +2165,12 @@
       </c>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="4"/>
+      <c r="A57" s="3"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
@@ -2229,12 +2187,12 @@
       </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="4"/>
+      <c r="A58" s="3"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
@@ -2251,12 +2209,12 @@
       </c>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="4"/>
+      <c r="A59" s="3"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
@@ -2273,12 +2231,12 @@
       </c>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="4"/>
+      <c r="A60" s="3"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
@@ -2295,12 +2253,12 @@
       </c>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="4"/>
+      <c r="A61" s="3"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
@@ -2317,699 +2275,699 @@
       </c>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+      <c r="A62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="A63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
+      <c r="A64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
+      <c r="A65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
+      <c r="A66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
+      <c r="A67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
+      <c r="A68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
+      <c r="A69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
+      <c r="A70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+      <c r="A71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
+      <c r="A72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
+      <c r="A73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
+      <c r="A74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
+      <c r="A75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
+      <c r="A76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
+      <c r="A77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
+      <c r="A78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
+      <c r="A79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
+      <c r="A80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
+      <c r="A81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
+      <c r="A82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
+      <c r="A83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
+      <c r="A84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
+      <c r="A85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
+      <c r="A86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
+      <c r="A87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
+      <c r="A88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
+      <c r="A89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
+      <c r="A90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
+      <c r="A91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
+      <c r="A92" s="4"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="4"/>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
+      <c r="A93" s="4"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
+      <c r="A94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
+      <c r="A95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
+      <c r="A96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
+      <c r="A97" s="4"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
+      <c r="A98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
+      <c r="A99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
+      <c r="A100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
+      <c r="A101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
+      <c r="A102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
+      <c r="A103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
+      <c r="A104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
+      <c r="A105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
+      <c r="A106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
+      <c r="A107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
+      <c r="A108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
+      <c r="A109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
+      <c r="A110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
     </row>
     <row r="111" spans="1:6">
-      <c r="A111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
+      <c r="A111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
     </row>
     <row r="112" spans="1:6">
-      <c r="A112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
+      <c r="A112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
+      <c r="A113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
     </row>
     <row r="114" spans="1:6">
-      <c r="A114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
+      <c r="A114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
     </row>
     <row r="115" spans="1:6">
-      <c r="A115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
+      <c r="A115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
+      <c r="A116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
     </row>
     <row r="117" spans="1:6">
-      <c r="A117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
+      <c r="A117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
     </row>
     <row r="118" spans="1:6">
-      <c r="A118" s="5"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="5"/>
+      <c r="A118" s="4"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4"/>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
+      <c r="A119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="5"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
+      <c r="A120" s="4"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4"/>
     </row>
     <row r="121" spans="1:6">
-      <c r="A121" s="5"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
+      <c r="A121" s="4"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4"/>
     </row>
     <row r="122" spans="1:6">
-      <c r="A122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
+      <c r="A122" s="4"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="A123" s="5"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="5"/>
+      <c r="A123" s="4"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4"/>
     </row>
     <row r="124" spans="1:6">
-      <c r="A124" s="5"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="5"/>
+      <c r="A124" s="4"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4"/>
     </row>
     <row r="125" spans="1:6">
-      <c r="A125" s="5"/>
-      <c r="E125" s="5"/>
-      <c r="F125" s="5"/>
+      <c r="A125" s="4"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4"/>
     </row>
     <row r="126" spans="1:6">
-      <c r="A126" s="5"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="5"/>
+      <c r="A126" s="4"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="5"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
+      <c r="A127" s="4"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="5"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="5"/>
+      <c r="A128" s="4"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4"/>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="5"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
+      <c r="A129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
     </row>
     <row r="130" spans="1:6">
-      <c r="A130" s="5"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="5"/>
+      <c r="A130" s="4"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="A131" s="5"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="5"/>
+      <c r="A131" s="4"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="5"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="5"/>
+      <c r="A132" s="4"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="4"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="A133" s="5"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="5"/>
+      <c r="A133" s="4"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
     </row>
     <row r="134" spans="1:6">
-      <c r="A134" s="5"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="5"/>
+      <c r="A134" s="4"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4"/>
     </row>
     <row r="135" spans="1:6">
-      <c r="A135" s="5"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="5"/>
+      <c r="A135" s="4"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
     </row>
     <row r="136" spans="1:6">
-      <c r="A136" s="5"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="5"/>
+      <c r="A136" s="4"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4"/>
     </row>
     <row r="137" spans="1:6">
-      <c r="A137" s="5"/>
-      <c r="E137" s="5"/>
-      <c r="F137" s="5"/>
+      <c r="A137" s="4"/>
+      <c r="E137" s="4"/>
+      <c r="F137" s="4"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="A138" s="5"/>
-      <c r="E138" s="5"/>
-      <c r="F138" s="5"/>
+      <c r="A138" s="4"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="A139" s="5"/>
-      <c r="E139" s="5"/>
-      <c r="F139" s="5"/>
+      <c r="A139" s="4"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
     </row>
     <row r="140" spans="1:6">
-      <c r="A140" s="5"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="5"/>
+      <c r="A140" s="4"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="4"/>
     </row>
     <row r="141" spans="1:6">
-      <c r="A141" s="5"/>
-      <c r="E141" s="5"/>
-      <c r="F141" s="5"/>
+      <c r="A141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4"/>
     </row>
     <row r="142" spans="1:6">
-      <c r="A142" s="5"/>
-      <c r="E142" s="5"/>
-      <c r="F142" s="5"/>
+      <c r="A142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
     </row>
     <row r="143" spans="1:6">
-      <c r="A143" s="5"/>
-      <c r="E143" s="5"/>
-      <c r="F143" s="5"/>
+      <c r="A143" s="4"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="A144" s="5"/>
-      <c r="E144" s="5"/>
-      <c r="F144" s="5"/>
+      <c r="A144" s="4"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
     </row>
     <row r="145" spans="1:6">
-      <c r="A145" s="5"/>
-      <c r="E145" s="5"/>
-      <c r="F145" s="5"/>
+      <c r="A145" s="4"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4"/>
     </row>
     <row r="146" spans="1:6">
-      <c r="A146" s="5"/>
-      <c r="E146" s="5"/>
-      <c r="F146" s="5"/>
+      <c r="A146" s="4"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4"/>
     </row>
     <row r="147" spans="1:6">
-      <c r="A147" s="5"/>
-      <c r="E147" s="5"/>
-      <c r="F147" s="5"/>
+      <c r="A147" s="4"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4"/>
     </row>
     <row r="148" spans="1:6">
-      <c r="A148" s="5"/>
-      <c r="E148" s="5"/>
-      <c r="F148" s="5"/>
+      <c r="A148" s="4"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="A149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="5"/>
+      <c r="A149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="A150" s="5"/>
-      <c r="E150" s="5"/>
-      <c r="F150" s="5"/>
+      <c r="A150" s="4"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4"/>
     </row>
     <row r="151" spans="1:6">
-      <c r="A151" s="5"/>
-      <c r="E151" s="5"/>
-      <c r="F151" s="5"/>
+      <c r="A151" s="4"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4"/>
     </row>
     <row r="152" spans="1:6">
-      <c r="A152" s="5"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
+      <c r="A152" s="4"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4"/>
     </row>
     <row r="153" spans="1:6">
-      <c r="A153" s="5"/>
-      <c r="E153" s="5"/>
-      <c r="F153" s="5"/>
+      <c r="A153" s="4"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6">
-      <c r="A154" s="5"/>
-      <c r="E154" s="5"/>
-      <c r="F154" s="5"/>
+      <c r="A154" s="4"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4"/>
     </row>
     <row r="155" spans="1:6">
-      <c r="A155" s="5"/>
-      <c r="E155" s="5"/>
-      <c r="F155" s="5"/>
+      <c r="A155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
     </row>
     <row r="156" spans="1:6">
-      <c r="A156" s="5"/>
-      <c r="E156" s="5"/>
-      <c r="F156" s="5"/>
+      <c r="A156" s="4"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="4"/>
     </row>
     <row r="157" spans="1:6">
-      <c r="A157" s="5"/>
-      <c r="E157" s="5"/>
-      <c r="F157" s="5"/>
+      <c r="A157" s="4"/>
+      <c r="E157" s="4"/>
+      <c r="F157" s="4"/>
     </row>
     <row r="158" spans="1:6">
-      <c r="A158" s="5"/>
-      <c r="E158" s="5"/>
-      <c r="F158" s="5"/>
+      <c r="A158" s="4"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="4"/>
     </row>
     <row r="159" spans="1:6">
-      <c r="A159" s="5"/>
-      <c r="E159" s="5"/>
-      <c r="F159" s="5"/>
+      <c r="A159" s="4"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="4"/>
     </row>
     <row r="160" spans="1:6">
-      <c r="A160" s="5"/>
-      <c r="E160" s="5"/>
-      <c r="F160" s="5"/>
+      <c r="A160" s="4"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4"/>
     </row>
     <row r="161" spans="1:6">
-      <c r="A161" s="5"/>
-      <c r="E161" s="5"/>
-      <c r="F161" s="5"/>
+      <c r="A161" s="4"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4"/>
     </row>
     <row r="162" spans="1:6">
-      <c r="A162" s="5"/>
-      <c r="E162" s="5"/>
-      <c r="F162" s="5"/>
+      <c r="A162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
     </row>
     <row r="163" spans="1:6">
-      <c r="A163" s="5"/>
-      <c r="E163" s="5"/>
-      <c r="F163" s="5"/>
+      <c r="A163" s="4"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="4"/>
     </row>
     <row r="164" spans="1:6">
-      <c r="A164" s="5"/>
-      <c r="E164" s="5"/>
-      <c r="F164" s="5"/>
+      <c r="A164" s="4"/>
+      <c r="E164" s="4"/>
+      <c r="F164" s="4"/>
     </row>
     <row r="165" spans="1:6">
-      <c r="A165" s="5"/>
-      <c r="E165" s="5"/>
-      <c r="F165" s="5"/>
+      <c r="A165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="4"/>
     </row>
     <row r="166" spans="1:6">
-      <c r="A166" s="5"/>
-      <c r="E166" s="5"/>
-      <c r="F166" s="5"/>
+      <c r="A166" s="4"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4"/>
     </row>
     <row r="167" spans="1:6">
-      <c r="A167" s="5"/>
-      <c r="E167" s="5"/>
-      <c r="F167" s="5"/>
+      <c r="A167" s="4"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="4"/>
     </row>
     <row r="168" spans="1:6">
-      <c r="A168" s="5"/>
-      <c r="E168" s="5"/>
-      <c r="F168" s="5"/>
+      <c r="A168" s="4"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="4"/>
     </row>
     <row r="169" spans="1:6">
-      <c r="A169" s="5"/>
-      <c r="E169" s="5"/>
-      <c r="F169" s="5"/>
+      <c r="A169" s="4"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="4"/>
     </row>
     <row r="170" spans="1:6">
-      <c r="A170" s="5"/>
-      <c r="E170" s="5"/>
-      <c r="F170" s="5"/>
+      <c r="A170" s="4"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="4"/>
     </row>
     <row r="171" spans="1:6">
-      <c r="A171" s="5"/>
-      <c r="E171" s="5"/>
-      <c r="F171" s="5"/>
+      <c r="A171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
     </row>
     <row r="172" spans="1:6">
-      <c r="A172" s="5"/>
-      <c r="E172" s="5"/>
-      <c r="F172" s="5"/>
+      <c r="A172" s="4"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="4"/>
     </row>
     <row r="173" spans="1:6">
-      <c r="A173" s="5"/>
-      <c r="E173" s="5"/>
-      <c r="F173" s="5"/>
+      <c r="A173" s="4"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="4"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="A174" s="5"/>
-      <c r="E174" s="5"/>
-      <c r="F174" s="5"/>
+      <c r="A174" s="4"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="4"/>
     </row>
     <row r="175" spans="1:6">
-      <c r="A175" s="5"/>
-      <c r="E175" s="5"/>
-      <c r="F175" s="5"/>
+      <c r="A175" s="4"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="4"/>
     </row>
     <row r="176" spans="1:6">
-      <c r="A176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5"/>
+      <c r="A176" s="4"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4"/>
     </row>
     <row r="177" spans="1:6">
-      <c r="A177" s="5"/>
-      <c r="E177" s="5"/>
-      <c r="F177" s="5"/>
+      <c r="A177" s="4"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="4"/>
     </row>
     <row r="178" spans="1:6">
-      <c r="A178" s="5"/>
-      <c r="E178" s="5"/>
-      <c r="F178" s="5"/>
+      <c r="A178" s="4"/>
+      <c r="E178" s="4"/>
+      <c r="F178" s="4"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="A179" s="5"/>
-      <c r="E179" s="5"/>
-      <c r="F179" s="5"/>
+      <c r="A179" s="4"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="4"/>
     </row>
     <row r="180" spans="1:6">
-      <c r="A180" s="5"/>
-      <c r="E180" s="5"/>
-      <c r="F180" s="5"/>
+      <c r="A180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4"/>
     </row>
     <row r="181" spans="1:6">
-      <c r="A181" s="5"/>
-      <c r="E181" s="5"/>
-      <c r="F181" s="5"/>
+      <c r="A181" s="4"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="4"/>
     </row>
     <row r="182" spans="1:6">
-      <c r="A182" s="5"/>
-      <c r="E182" s="5"/>
-      <c r="F182" s="5"/>
+      <c r="A182" s="4"/>
+      <c r="E182" s="4"/>
+      <c r="F182" s="4"/>
     </row>
     <row r="183" spans="1:6">
-      <c r="A183" s="5"/>
-      <c r="E183" s="5"/>
-      <c r="F183" s="5"/>
+      <c r="A183" s="4"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="4"/>
     </row>
     <row r="184" spans="1:6">
-      <c r="A184" s="5"/>
-      <c r="E184" s="5"/>
-      <c r="F184" s="5"/>
+      <c r="A184" s="4"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="4"/>
     </row>
     <row r="185" spans="1:6">
-      <c r="A185" s="5"/>
-      <c r="E185" s="5"/>
-      <c r="F185" s="5"/>
+      <c r="A185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
     </row>
     <row r="186" spans="1:6">
-      <c r="A186" s="5"/>
-      <c r="E186" s="5"/>
-      <c r="F186" s="5"/>
+      <c r="A186" s="4"/>
+      <c r="E186" s="4"/>
+      <c r="F186" s="4"/>
     </row>
     <row r="187" spans="1:6">
-      <c r="A187" s="5"/>
-      <c r="E187" s="5"/>
-      <c r="F187" s="5"/>
+      <c r="A187" s="4"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="4"/>
     </row>
     <row r="188" spans="1:6">
-      <c r="A188" s="5"/>
-      <c r="E188" s="5"/>
-      <c r="F188" s="5"/>
+      <c r="A188" s="4"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="4"/>
     </row>
     <row r="189" spans="1:6">
-      <c r="A189" s="5"/>
-      <c r="E189" s="5"/>
-      <c r="F189" s="5"/>
+      <c r="A189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
     </row>
     <row r="190" spans="1:6">
-      <c r="A190" s="5"/>
-      <c r="E190" s="5"/>
-      <c r="F190" s="5"/>
+      <c r="A190" s="4"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="4"/>
     </row>
     <row r="191" spans="1:6">
-      <c r="A191" s="5"/>
-      <c r="E191" s="5"/>
-      <c r="F191" s="5"/>
+      <c r="A191" s="4"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="4"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="A192" s="5"/>
-      <c r="E192" s="5"/>
-      <c r="F192" s="5"/>
+      <c r="A192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4"/>
     </row>
     <row r="193" spans="1:6">
-      <c r="A193" s="5"/>
-      <c r="E193" s="5"/>
-      <c r="F193" s="5"/>
+      <c r="A193" s="4"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="4"/>
     </row>
     <row r="194" spans="1:6">
-      <c r="A194" s="5"/>
-      <c r="E194" s="5"/>
-      <c r="F194" s="5"/>
+      <c r="A194" s="4"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4"/>
     </row>
     <row r="195" spans="1:6">
-      <c r="A195" s="5"/>
-      <c r="E195" s="5"/>
-      <c r="F195" s="5"/>
+      <c r="A195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
     </row>
     <row r="196" spans="1:6">
-      <c r="A196" s="5"/>
-      <c r="E196" s="5"/>
-      <c r="F196" s="5"/>
+      <c r="A196" s="4"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4"/>
     </row>
     <row r="197" spans="1:6">
-      <c r="A197" s="5"/>
-      <c r="E197" s="5"/>
-      <c r="F197" s="5"/>
+      <c r="A197" s="4"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
     </row>
     <row r="198" spans="1:6">
-      <c r="A198" s="5"/>
-      <c r="E198" s="5"/>
-      <c r="F198" s="5"/>
+      <c r="A198" s="4"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
     </row>
     <row r="199" spans="1:6">
-      <c r="A199" s="5"/>
-      <c r="E199" s="5"/>
-      <c r="F199" s="5"/>
+      <c r="A199" s="4"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4"/>
     </row>
     <row r="200" spans="1:6">
-      <c r="A200" s="5"/>
-      <c r="E200" s="5"/>
-      <c r="F200" s="5"/>
+      <c r="A200" s="4"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3902,62 +3860,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14"/>
-  <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18.649999999999999" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="18.649999999999999" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="18.649999999999999" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="13" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" ht="34" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="18.649999999999999" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="18.649999999999999" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="18.649999999999999" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="18.649999999999999" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>